--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.0253981305783962</v>
       </c>
       <c r="C2" t="n">
-        <v>118042668</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>118042668</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>79772405</v>
+        <v>3957576</v>
       </c>
       <c r="L2" t="n">
-        <v>44881644</v>
+        <v>2063647</v>
       </c>
       <c r="M2" t="n">
-        <v>11116406</v>
+        <v>479457</v>
       </c>
       <c r="N2" t="n">
-        <v>592515</v>
+        <v>20737</v>
       </c>
       <c r="O2" t="n">
-        <v>6746897</v>
+        <v>303524</v>
       </c>
       <c r="P2" t="n">
-        <v>2774895</v>
+        <v>130709</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999158978462219</v>
+        <v>0.9998834729194641</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8559851050376892</v>
+        <v>0.8068235516548157</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7232586145401001</v>
+        <v>0.6315381526947021</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6388248801231384</v>
+        <v>0.5244919657707214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4586782157421112</v>
+        <v>0.3063162863254547</v>
       </c>
       <c r="V2" t="n">
-        <v>0.696747899055481</v>
+        <v>0.595642626285553</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7581636905670166</v>
+        <v>0.6782608032226562</v>
       </c>
       <c r="X2" t="n">
-        <v>118042668</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>118042668</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>77802194</v>
+        <v>3879625</v>
       </c>
       <c r="AG2" t="n">
-        <v>41589706</v>
+        <v>1931326</v>
       </c>
       <c r="AH2" t="n">
-        <v>10122322</v>
+        <v>444442</v>
       </c>
       <c r="AI2" t="n">
-        <v>549693</v>
+        <v>19781</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6211683</v>
+        <v>281899</v>
       </c>
       <c r="AK2" t="n">
-        <v>2611312</v>
+        <v>123153</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8292971849441528</v>
+        <v>0.7857089638710022</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6831687092781067</v>
+        <v>0.6027695536613464</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5752609968185425</v>
+        <v>0.479902982711792</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3273576200008392</v>
+        <v>0.2238226681947708</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6434959173202515</v>
+        <v>0.5548602938652039</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7111421823501587</v>
+        <v>0.6372300982475281</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.006709646399966036</v>
       </c>
       <c r="C3" t="n">
-        <v>3023</v>
+        <v>209</v>
       </c>
       <c r="D3" t="n">
-        <v>79772405</v>
+        <v>3957576</v>
       </c>
       <c r="E3" t="n">
-        <v>12217298</v>
+        <v>859909</v>
       </c>
       <c r="F3" t="n">
-        <v>662568</v>
+        <v>43661</v>
       </c>
       <c r="G3" t="n">
-        <v>83350</v>
+        <v>5592</v>
       </c>
       <c r="H3" t="n">
-        <v>61409</v>
+        <v>3269</v>
       </c>
       <c r="I3" t="n">
-        <v>9766</v>
+        <v>376</v>
       </c>
       <c r="J3" t="n">
-        <v>187285006</v>
+        <v>9856904</v>
       </c>
       <c r="K3" t="n">
-        <v>199106503</v>
+        <v>10252252</v>
       </c>
       <c r="L3" t="n">
-        <v>226456511</v>
+        <v>11606628</v>
       </c>
       <c r="M3" t="n">
-        <v>281327434</v>
+        <v>14701113</v>
       </c>
       <c r="N3" t="n">
-        <v>302949699</v>
+        <v>15934473</v>
       </c>
       <c r="O3" t="n">
-        <v>292713930</v>
+        <v>15354162</v>
       </c>
       <c r="P3" t="n">
-        <v>300776347</v>
+        <v>15814890</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8595255017280579</v>
+        <v>0.8125451803207397</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7273233532905579</v>
+        <v>0.6330658197402954</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6271513700485229</v>
+        <v>0.5130032896995544</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3508854508399963</v>
+        <v>0.2330890446901321</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6964786648750305</v>
+        <v>0.5949258208274841</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7548419833183289</v>
+        <v>0.6754742860794067</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>77802194</v>
+        <v>3879625</v>
       </c>
       <c r="Z3" t="n">
-        <v>13702589</v>
+        <v>907451</v>
       </c>
       <c r="AA3" t="n">
-        <v>924207</v>
+        <v>61002</v>
       </c>
       <c r="AB3" t="n">
-        <v>283643</v>
+        <v>17272</v>
       </c>
       <c r="AC3" t="n">
-        <v>82706</v>
+        <v>4608</v>
       </c>
       <c r="AD3" t="n">
-        <v>14480</v>
+        <v>634</v>
       </c>
       <c r="AE3" t="n">
-        <v>187294932</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>196512953</v>
+        <v>10141695</v>
       </c>
       <c r="AG3" t="n">
-        <v>224341686</v>
+        <v>11537872</v>
       </c>
       <c r="AH3" t="n">
-        <v>280138634</v>
+        <v>14654126</v>
       </c>
       <c r="AI3" t="n">
-        <v>302519483</v>
+        <v>15912837</v>
       </c>
       <c r="AJ3" t="n">
-        <v>292209102</v>
+        <v>15334057</v>
       </c>
       <c r="AK3" t="n">
-        <v>300600788</v>
+        <v>15806783</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8382970094680786</v>
+        <v>0.7965407371520996</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6739763021469116</v>
+        <v>0.5924736261367798</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5710684061050415</v>
+        <v>0.4755384027957916</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3255264163017273</v>
+        <v>0.2223433703184128</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6412287950515747</v>
+        <v>0.5525394678115845</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7103432416915894</v>
+        <v>0.636426568031311</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.06292636329607457</v>
       </c>
       <c r="C4" t="n">
-        <v>1176</v>
+        <v>87</v>
       </c>
       <c r="D4" t="n">
-        <v>12447208</v>
+        <v>887758</v>
       </c>
       <c r="E4" t="n">
-        <v>44881644</v>
+        <v>2063647</v>
       </c>
       <c r="F4" t="n">
-        <v>3619617</v>
+        <v>254757</v>
       </c>
       <c r="G4" t="n">
-        <v>147625</v>
+        <v>10445</v>
       </c>
       <c r="H4" t="n">
-        <v>532894</v>
+        <v>38090</v>
       </c>
       <c r="I4" t="n">
-        <v>77803</v>
+        <v>4983</v>
       </c>
       <c r="J4" t="n">
-        <v>9926</v>
+        <v>724</v>
       </c>
       <c r="K4" t="n">
-        <v>13421278</v>
+        <v>947556</v>
       </c>
       <c r="L4" t="n">
-        <v>17173122</v>
+        <v>1204005</v>
       </c>
       <c r="M4" t="n">
-        <v>6284930</v>
+        <v>434679</v>
       </c>
       <c r="N4" t="n">
-        <v>699273</v>
+        <v>46961</v>
       </c>
       <c r="O4" t="n">
-        <v>2936515</v>
+        <v>206050</v>
       </c>
       <c r="P4" t="n">
-        <v>885126</v>
+        <v>62003</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999579787254333</v>
+        <v>0.9999417662620544</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8577516674995422</v>
+        <v>0.8096742033958435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7252852320671082</v>
+        <v>0.6323010921478271</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6329343318939209</v>
+        <v>0.5186840295791626</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3976055681705475</v>
+        <v>0.2647321820259094</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6966132521629333</v>
+        <v>0.5952839851379395</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7564991116523743</v>
+        <v>0.6768646836280823</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>14775728</v>
+        <v>981669</v>
       </c>
       <c r="Z4" t="n">
-        <v>41589706</v>
+        <v>1931326</v>
       </c>
       <c r="AA4" t="n">
-        <v>4289343</v>
+        <v>275114</v>
       </c>
       <c r="AB4" t="n">
-        <v>289612</v>
+        <v>18418</v>
       </c>
       <c r="AC4" t="n">
-        <v>661488</v>
+        <v>46413</v>
       </c>
       <c r="AD4" t="n">
-        <v>102090</v>
+        <v>6827</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>16014828</v>
+        <v>1058113</v>
       </c>
       <c r="AG4" t="n">
-        <v>19287947</v>
+        <v>1272761</v>
       </c>
       <c r="AH4" t="n">
-        <v>7473730</v>
+        <v>481666</v>
       </c>
       <c r="AI4" t="n">
-        <v>1129489</v>
+        <v>68597</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3441343</v>
+        <v>226155</v>
       </c>
       <c r="AK4" t="n">
-        <v>1060685</v>
+        <v>70110</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8337727785110474</v>
+        <v>0.791087806224823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.678541362285614</v>
+        <v>0.5975772738456726</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.573157012462616</v>
+        <v>0.4777107238769531</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3264394700527191</v>
+        <v>0.2230805605649948</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6423603892326355</v>
+        <v>0.5536974668502808</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7107424736022949</v>
+        <v>0.6368280649185181</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1870</v>
+        <v>139</v>
       </c>
       <c r="D5" t="n">
-        <v>684140</v>
+        <v>42566</v>
       </c>
       <c r="E5" t="n">
-        <v>4009139</v>
+        <v>277850</v>
       </c>
       <c r="F5" t="n">
-        <v>11116406</v>
+        <v>479457</v>
       </c>
       <c r="G5" t="n">
-        <v>256003</v>
+        <v>16980</v>
       </c>
       <c r="H5" t="n">
-        <v>1461423</v>
+        <v>103190</v>
       </c>
       <c r="I5" t="n">
-        <v>196255</v>
+        <v>14426</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13037414</v>
+        <v>913016</v>
       </c>
       <c r="L5" t="n">
-        <v>16826323</v>
+        <v>1196120</v>
       </c>
       <c r="M5" t="n">
-        <v>6608830</v>
+        <v>455151</v>
       </c>
       <c r="N5" t="n">
-        <v>1096113</v>
+        <v>68229</v>
       </c>
       <c r="O5" t="n">
-        <v>2940258</v>
+        <v>206664</v>
       </c>
       <c r="P5" t="n">
-        <v>901232</v>
+        <v>62798</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999675154685974</v>
+        <v>0.9999549388885498</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9133461117744446</v>
+        <v>0.8842236399650574</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8886496424674988</v>
+        <v>0.850649356842041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9577721357345581</v>
+        <v>0.9446292519569397</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9941200017929077</v>
+        <v>0.9928321838378906</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9807531833648682</v>
+        <v>0.9743183851242065</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9941495656967163</v>
+        <v>0.9922341108322144</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>876381</v>
+        <v>55693</v>
       </c>
       <c r="Z5" t="n">
-        <v>4475546</v>
+        <v>288452</v>
       </c>
       <c r="AA5" t="n">
-        <v>10122322</v>
+        <v>444442</v>
       </c>
       <c r="AB5" t="n">
-        <v>311939</v>
+        <v>18491</v>
       </c>
       <c r="AC5" t="n">
-        <v>1696191</v>
+        <v>110393</v>
       </c>
       <c r="AD5" t="n">
-        <v>242857</v>
+        <v>17137</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>15007625</v>
+        <v>990967</v>
       </c>
       <c r="AG5" t="n">
-        <v>20118261</v>
+        <v>1328441</v>
       </c>
       <c r="AH5" t="n">
-        <v>7602914</v>
+        <v>490166</v>
       </c>
       <c r="AI5" t="n">
-        <v>1138935</v>
+        <v>69185</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3475472</v>
+        <v>228289</v>
       </c>
       <c r="AK5" t="n">
-        <v>1064815</v>
+        <v>70354</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8983994722366333</v>
+        <v>0.8724935054779053</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8709421753883362</v>
+        <v>0.8381370902061462</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9506230354309082</v>
+        <v>0.9395265579223633</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9925707578659058</v>
+        <v>0.9914263486862183</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9773470163345337</v>
+        <v>0.9717216491699219</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9930388331413269</v>
+        <v>0.9912594556808472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2637</v>
+        <v>202</v>
       </c>
       <c r="D6" t="n">
-        <v>218560</v>
+        <v>14300</v>
       </c>
       <c r="E6" t="n">
-        <v>304856</v>
+        <v>20160</v>
       </c>
       <c r="F6" t="n">
-        <v>342519</v>
+        <v>18681</v>
       </c>
       <c r="G6" t="n">
-        <v>592515</v>
+        <v>20737</v>
       </c>
       <c r="H6" t="n">
-        <v>194340</v>
+        <v>12498</v>
       </c>
       <c r="I6" t="n">
-        <v>33201</v>
+        <v>2388</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>258670</v>
+        <v>15475</v>
       </c>
       <c r="Z6" t="n">
-        <v>305262</v>
+        <v>19911</v>
       </c>
       <c r="AA6" t="n">
-        <v>322172</v>
+        <v>18620</v>
       </c>
       <c r="AB6" t="n">
-        <v>549693</v>
+        <v>19781</v>
       </c>
       <c r="AC6" t="n">
-        <v>214238</v>
+        <v>12539</v>
       </c>
       <c r="AD6" t="n">
-        <v>38593</v>
+        <v>2640</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>769</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>66503</v>
+        <v>2849</v>
       </c>
       <c r="E7" t="n">
-        <v>583079</v>
+        <v>42462</v>
       </c>
       <c r="F7" t="n">
-        <v>1534508</v>
+        <v>109327</v>
       </c>
       <c r="G7" t="n">
-        <v>187298</v>
+        <v>12135</v>
       </c>
       <c r="H7" t="n">
-        <v>6746897</v>
+        <v>303524</v>
       </c>
       <c r="I7" t="n">
-        <v>568101</v>
+        <v>39830</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>95960</v>
+        <v>5163</v>
       </c>
       <c r="Z7" t="n">
-        <v>727669</v>
+        <v>51800</v>
       </c>
       <c r="AA7" t="n">
-        <v>1776468</v>
+        <v>116271</v>
       </c>
       <c r="AB7" t="n">
-        <v>212710</v>
+        <v>12183</v>
       </c>
       <c r="AC7" t="n">
-        <v>6211683</v>
+        <v>281899</v>
       </c>
       <c r="AD7" t="n">
-        <v>662665</v>
+        <v>42872</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>451</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>4867</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
-        <v>58750</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="n">
-        <v>125718</v>
+        <v>8253</v>
       </c>
       <c r="G8" t="n">
-        <v>24997</v>
+        <v>1809</v>
       </c>
       <c r="H8" t="n">
-        <v>686449</v>
+        <v>49003</v>
       </c>
       <c r="I8" t="n">
-        <v>2774895</v>
+        <v>130709</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8089</v>
+        <v>113</v>
       </c>
       <c r="Z8" t="n">
-        <v>76881</v>
+        <v>5147</v>
       </c>
       <c r="AA8" t="n">
-        <v>161540</v>
+        <v>10659</v>
       </c>
       <c r="AB8" t="n">
-        <v>31585</v>
+        <v>2233</v>
       </c>
       <c r="AC8" t="n">
-        <v>786720</v>
+        <v>52202</v>
       </c>
       <c r="AD8" t="n">
-        <v>2611312</v>
+        <v>123153</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
